--- a/tests/fixtures/test.xlsx
+++ b/tests/fixtures/test.xlsx
@@ -525,7 +525,7 @@
         <v>3.2</v>
       </c>
       <c r="D3" s="4">
-        <v>46234.66666666667</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="4" ht="40" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -539,7 +539,7 @@
         <v>5.5</v>
       </c>
       <c r="D4" s="4">
-        <v>46235.66666666667</v>
+        <v>46236</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -553,7 +553,7 @@
         <v>1.5</v>
       </c>
       <c r="D5" s="4">
-        <v>46236.66666666667</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -565,7 +565,7 @@
         <v>2.5</v>
       </c>
       <c r="D6" s="4">
-        <v>46237.66666666667</v>
+        <v>46238</v>
       </c>
     </row>
   </sheetData>
